--- a/artfynd/A 24824-2025 artfynd.xlsx
+++ b/artfynd/A 24824-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>126017473</v>
       </c>
       <c r="B2" t="n">
-        <v>97216</v>
+        <v>97218</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -996,7 +996,7 @@
         <v>126017474</v>
       </c>
       <c r="B5" t="n">
-        <v>98332</v>
+        <v>98334</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>

--- a/artfynd/A 24824-2025 artfynd.xlsx
+++ b/artfynd/A 24824-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>126017473</v>
       </c>
       <c r="B2" t="n">
-        <v>97218</v>
+        <v>97222</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -784,7 +784,7 @@
         <v>126017472</v>
       </c>
       <c r="B3" t="n">
-        <v>80071</v>
+        <v>80075</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -890,7 +890,7 @@
         <v>126017471</v>
       </c>
       <c r="B4" t="n">
-        <v>80072</v>
+        <v>80076</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -996,7 +996,7 @@
         <v>126017474</v>
       </c>
       <c r="B5" t="n">
-        <v>98334</v>
+        <v>98338</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>

--- a/artfynd/A 24824-2025 artfynd.xlsx
+++ b/artfynd/A 24824-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>126017473</v>
       </c>
       <c r="B2" t="n">
-        <v>97222</v>
+        <v>97223</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -781,10 +781,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>126017472</v>
+        <v>126017471</v>
       </c>
       <c r="B3" t="n">
-        <v>80075</v>
+        <v>80076</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -792,21 +792,21 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>6458</v>
+        <v>2081</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
@@ -820,10 +820,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>482470</v>
+        <v>482483</v>
       </c>
       <c r="R3" t="n">
-        <v>6840129</v>
+        <v>6840105</v>
       </c>
       <c r="S3" t="n">
         <v>5</v>
@@ -887,10 +887,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>126017471</v>
+        <v>126017472</v>
       </c>
       <c r="B4" t="n">
-        <v>80076</v>
+        <v>80075</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -898,21 +898,21 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>2081</v>
+        <v>6458</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
@@ -926,10 +926,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>482483</v>
+        <v>482470</v>
       </c>
       <c r="R4" t="n">
-        <v>6840105</v>
+        <v>6840129</v>
       </c>
       <c r="S4" t="n">
         <v>5</v>
@@ -996,7 +996,7 @@
         <v>126017474</v>
       </c>
       <c r="B5" t="n">
-        <v>98338</v>
+        <v>98339</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>

--- a/artfynd/A 24824-2025 artfynd.xlsx
+++ b/artfynd/A 24824-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY5"/>
+  <dimension ref="A1:AY7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1097,6 +1097,200 @@
       </c>
       <c r="AY5" t="inlineStr"/>
     </row>
+    <row r="6">
+      <c r="A6" t="n">
+        <v>126172019</v>
+      </c>
+      <c r="B6" t="n">
+        <v>78972</v>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E6" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr"/>
+      <c r="P6" t="inlineStr">
+        <is>
+          <t>Tallåstjärnen, Tallåstjärnen, Dlr</t>
+        </is>
+      </c>
+      <c r="Q6" t="n">
+        <v>482420</v>
+      </c>
+      <c r="R6" t="n">
+        <v>6840070</v>
+      </c>
+      <c r="S6" t="n">
+        <v>10</v>
+      </c>
+      <c r="T6" t="inlineStr">
+        <is>
+          <t>Gävleborg</t>
+        </is>
+      </c>
+      <c r="U6" t="inlineStr">
+        <is>
+          <t>Ljusdal</t>
+        </is>
+      </c>
+      <c r="V6" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W6" t="inlineStr">
+        <is>
+          <t>Los</t>
+        </is>
+      </c>
+      <c r="Y6" t="inlineStr">
+        <is>
+          <t>2025-06-23</t>
+        </is>
+      </c>
+      <c r="AA6" t="inlineStr">
+        <is>
+          <t>2025-06-23</t>
+        </is>
+      </c>
+      <c r="AD6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT6" t="inlineStr"/>
+      <c r="AW6" t="inlineStr">
+        <is>
+          <t>Anders Heggestad</t>
+        </is>
+      </c>
+      <c r="AX6" t="inlineStr">
+        <is>
+          <t>Anders Heggestad</t>
+        </is>
+      </c>
+      <c r="AY6" t="inlineStr"/>
+    </row>
+    <row r="7">
+      <c r="A7" t="n">
+        <v>126171881</v>
+      </c>
+      <c r="B7" t="n">
+        <v>80075</v>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E7" t="n">
+        <v>6458</v>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>Lunglav</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>Lobaria pulmonaria</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr"/>
+      <c r="P7" t="inlineStr">
+        <is>
+          <t>Tallåstjärnen, Tallåstjärnen, Dlr</t>
+        </is>
+      </c>
+      <c r="Q7" t="n">
+        <v>482488</v>
+      </c>
+      <c r="R7" t="n">
+        <v>6840108</v>
+      </c>
+      <c r="S7" t="n">
+        <v>10</v>
+      </c>
+      <c r="T7" t="inlineStr">
+        <is>
+          <t>Gävleborg</t>
+        </is>
+      </c>
+      <c r="U7" t="inlineStr">
+        <is>
+          <t>Ljusdal</t>
+        </is>
+      </c>
+      <c r="V7" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W7" t="inlineStr">
+        <is>
+          <t>Los</t>
+        </is>
+      </c>
+      <c r="Y7" t="inlineStr">
+        <is>
+          <t>2025-06-23</t>
+        </is>
+      </c>
+      <c r="AA7" t="inlineStr">
+        <is>
+          <t>2025-06-23</t>
+        </is>
+      </c>
+      <c r="AD7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT7" t="inlineStr"/>
+      <c r="AW7" t="inlineStr">
+        <is>
+          <t>Anders Heggestad</t>
+        </is>
+      </c>
+      <c r="AX7" t="inlineStr">
+        <is>
+          <t>Anders Heggestad</t>
+        </is>
+      </c>
+      <c r="AY7" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 24824-2025 artfynd.xlsx
+++ b/artfynd/A 24824-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>126017473</v>
       </c>
       <c r="B2" t="n">
-        <v>97223</v>
+        <v>97225</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -784,7 +784,7 @@
         <v>126017471</v>
       </c>
       <c r="B3" t="n">
-        <v>80076</v>
+        <v>80077</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -890,7 +890,7 @@
         <v>126017472</v>
       </c>
       <c r="B4" t="n">
-        <v>80075</v>
+        <v>80076</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -996,7 +996,7 @@
         <v>126017474</v>
       </c>
       <c r="B5" t="n">
-        <v>98339</v>
+        <v>98341</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1102,7 +1102,7 @@
         <v>126172019</v>
       </c>
       <c r="B6" t="n">
-        <v>78972</v>
+        <v>78973</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1199,7 +1199,7 @@
         <v>126171881</v>
       </c>
       <c r="B7" t="n">
-        <v>80075</v>
+        <v>80076</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>

--- a/artfynd/A 24824-2025 artfynd.xlsx
+++ b/artfynd/A 24824-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>126017473</v>
       </c>
       <c r="B2" t="n">
-        <v>97225</v>
+        <v>97227</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -996,7 +996,7 @@
         <v>126017474</v>
       </c>
       <c r="B5" t="n">
-        <v>98341</v>
+        <v>98343</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>

--- a/artfynd/A 24824-2025 artfynd.xlsx
+++ b/artfynd/A 24824-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>126017473</v>
       </c>
       <c r="B2" t="n">
-        <v>97227</v>
+        <v>97229</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -996,7 +996,7 @@
         <v>126017474</v>
       </c>
       <c r="B5" t="n">
-        <v>98343</v>
+        <v>98345</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>

--- a/artfynd/A 24824-2025 artfynd.xlsx
+++ b/artfynd/A 24824-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>126017473</v>
       </c>
       <c r="B2" t="n">
-        <v>97229</v>
+        <v>97233</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -781,10 +781,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>126017471</v>
+        <v>126017472</v>
       </c>
       <c r="B3" t="n">
-        <v>80077</v>
+        <v>80080</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -792,21 +792,21 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>2081</v>
+        <v>6458</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
@@ -820,10 +820,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>482483</v>
+        <v>482470</v>
       </c>
       <c r="R3" t="n">
-        <v>6840105</v>
+        <v>6840129</v>
       </c>
       <c r="S3" t="n">
         <v>5</v>
@@ -887,10 +887,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>126017472</v>
+        <v>126017471</v>
       </c>
       <c r="B4" t="n">
-        <v>80076</v>
+        <v>80081</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -898,21 +898,21 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>6458</v>
+        <v>2081</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
@@ -926,10 +926,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>482470</v>
+        <v>482483</v>
       </c>
       <c r="R4" t="n">
-        <v>6840129</v>
+        <v>6840105</v>
       </c>
       <c r="S4" t="n">
         <v>5</v>
@@ -996,7 +996,7 @@
         <v>126017474</v>
       </c>
       <c r="B5" t="n">
-        <v>98345</v>
+        <v>98349</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1102,7 +1102,7 @@
         <v>126172019</v>
       </c>
       <c r="B6" t="n">
-        <v>78973</v>
+        <v>78977</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1199,7 +1199,7 @@
         <v>126171881</v>
       </c>
       <c r="B7" t="n">
-        <v>80076</v>
+        <v>80080</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>

--- a/artfynd/A 24824-2025 artfynd.xlsx
+++ b/artfynd/A 24824-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>126017473</v>
       </c>
       <c r="B2" t="n">
-        <v>97233</v>
+        <v>97236</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -996,7 +996,7 @@
         <v>126017474</v>
       </c>
       <c r="B5" t="n">
-        <v>98349</v>
+        <v>98352</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>

--- a/artfynd/A 24824-2025 artfynd.xlsx
+++ b/artfynd/A 24824-2025 artfynd.xlsx
@@ -781,10 +781,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>126017472</v>
+        <v>126017471</v>
       </c>
       <c r="B3" t="n">
-        <v>80080</v>
+        <v>80081</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -792,21 +792,21 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>6458</v>
+        <v>2081</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
@@ -820,10 +820,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>482470</v>
+        <v>482483</v>
       </c>
       <c r="R3" t="n">
-        <v>6840129</v>
+        <v>6840105</v>
       </c>
       <c r="S3" t="n">
         <v>5</v>
@@ -887,10 +887,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>126017471</v>
+        <v>126017472</v>
       </c>
       <c r="B4" t="n">
-        <v>80081</v>
+        <v>80080</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -898,21 +898,21 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>2081</v>
+        <v>6458</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
@@ -926,10 +926,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>482483</v>
+        <v>482470</v>
       </c>
       <c r="R4" t="n">
-        <v>6840105</v>
+        <v>6840129</v>
       </c>
       <c r="S4" t="n">
         <v>5</v>

--- a/artfynd/A 24824-2025 artfynd.xlsx
+++ b/artfynd/A 24824-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>126017473</v>
       </c>
       <c r="B2" t="n">
-        <v>97236</v>
+        <v>97245</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -784,7 +784,7 @@
         <v>126017471</v>
       </c>
       <c r="B3" t="n">
-        <v>80081</v>
+        <v>80084</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -890,7 +890,7 @@
         <v>126017472</v>
       </c>
       <c r="B4" t="n">
-        <v>80080</v>
+        <v>80083</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -996,7 +996,7 @@
         <v>126017474</v>
       </c>
       <c r="B5" t="n">
-        <v>98352</v>
+        <v>98361</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1102,7 +1102,7 @@
         <v>126172019</v>
       </c>
       <c r="B6" t="n">
-        <v>78977</v>
+        <v>78980</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1199,7 +1199,7 @@
         <v>126171881</v>
       </c>
       <c r="B7" t="n">
-        <v>80080</v>
+        <v>80083</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>

--- a/artfynd/A 24824-2025 artfynd.xlsx
+++ b/artfynd/A 24824-2025 artfynd.xlsx
@@ -781,10 +781,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>126017471</v>
+        <v>126017472</v>
       </c>
       <c r="B3" t="n">
-        <v>80084</v>
+        <v>80083</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -792,21 +792,21 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>2081</v>
+        <v>6458</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
@@ -820,10 +820,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>482483</v>
+        <v>482470</v>
       </c>
       <c r="R3" t="n">
-        <v>6840105</v>
+        <v>6840129</v>
       </c>
       <c r="S3" t="n">
         <v>5</v>
@@ -887,10 +887,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>126017472</v>
+        <v>126017471</v>
       </c>
       <c r="B4" t="n">
-        <v>80083</v>
+        <v>80084</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -898,21 +898,21 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>6458</v>
+        <v>2081</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
@@ -926,10 +926,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>482470</v>
+        <v>482483</v>
       </c>
       <c r="R4" t="n">
-        <v>6840129</v>
+        <v>6840105</v>
       </c>
       <c r="S4" t="n">
         <v>5</v>

--- a/artfynd/A 24824-2025 artfynd.xlsx
+++ b/artfynd/A 24824-2025 artfynd.xlsx
@@ -781,10 +781,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>126017472</v>
+        <v>126017471</v>
       </c>
       <c r="B3" t="n">
-        <v>80083</v>
+        <v>80084</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -792,21 +792,21 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>6458</v>
+        <v>2081</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
@@ -820,10 +820,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>482470</v>
+        <v>482483</v>
       </c>
       <c r="R3" t="n">
-        <v>6840129</v>
+        <v>6840105</v>
       </c>
       <c r="S3" t="n">
         <v>5</v>
@@ -887,10 +887,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>126017471</v>
+        <v>126017472</v>
       </c>
       <c r="B4" t="n">
-        <v>80084</v>
+        <v>80083</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -898,21 +898,21 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>2081</v>
+        <v>6458</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
@@ -926,10 +926,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>482483</v>
+        <v>482470</v>
       </c>
       <c r="R4" t="n">
-        <v>6840105</v>
+        <v>6840129</v>
       </c>
       <c r="S4" t="n">
         <v>5</v>
